--- a/inputs/nodes.xlsx
+++ b/inputs/nodes.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\Er\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>node_id</t>
   </si>
@@ -65,13 +70,43 @@
   </si>
   <si>
     <t>N15</t>
+  </si>
+  <si>
+    <t>N16</t>
+  </si>
+  <si>
+    <t>N17</t>
+  </si>
+  <si>
+    <t>N18</t>
+  </si>
+  <si>
+    <t>N19</t>
+  </si>
+  <si>
+    <t>N20</t>
+  </si>
+  <si>
+    <t>N21</t>
+  </si>
+  <si>
+    <t>N22</t>
+  </si>
+  <si>
+    <t>N23</t>
+  </si>
+  <si>
+    <t>N24</t>
+  </si>
+  <si>
+    <t>N25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,11 +169,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Teması">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -180,7 +223,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -212,9 +255,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -246,6 +290,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -421,93 +466,143 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/nodes.xlsx
+++ b/inputs/nodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>node_id</t>
   </si>
@@ -100,6 +100,21 @@
   </si>
   <si>
     <t>N25</t>
+  </si>
+  <si>
+    <t>N26</t>
+  </si>
+  <si>
+    <t>N27</t>
+  </si>
+  <si>
+    <t>N28</t>
+  </si>
+  <si>
+    <t>N29</t>
+  </si>
+  <si>
+    <t>N30</t>
   </si>
 </sst>
 </file>
@@ -467,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -605,6 +620,31 @@
         <v>26</v>
       </c>
     </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inputs/nodes.xlsx
+++ b/inputs/nodes.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\Er\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\GitHub\internal-logistics-model2\internal-logistics-model2\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>node_id</t>
   </si>
@@ -115,6 +115,96 @@
   </si>
   <si>
     <t>N30</t>
+  </si>
+  <si>
+    <t>N31</t>
+  </si>
+  <si>
+    <t>N32</t>
+  </si>
+  <si>
+    <t>N33</t>
+  </si>
+  <si>
+    <t>N34</t>
+  </si>
+  <si>
+    <t>N35</t>
+  </si>
+  <si>
+    <t>N36</t>
+  </si>
+  <si>
+    <t>N37</t>
+  </si>
+  <si>
+    <t>N38</t>
+  </si>
+  <si>
+    <t>N39</t>
+  </si>
+  <si>
+    <t>N40</t>
+  </si>
+  <si>
+    <t>N41</t>
+  </si>
+  <si>
+    <t>N42</t>
+  </si>
+  <si>
+    <t>N43</t>
+  </si>
+  <si>
+    <t>N44</t>
+  </si>
+  <si>
+    <t>N45</t>
+  </si>
+  <si>
+    <t>N46</t>
+  </si>
+  <si>
+    <t>N47</t>
+  </si>
+  <si>
+    <t>N48</t>
+  </si>
+  <si>
+    <t>N49</t>
+  </si>
+  <si>
+    <t>N50</t>
+  </si>
+  <si>
+    <t>N51</t>
+  </si>
+  <si>
+    <t>N52</t>
+  </si>
+  <si>
+    <t>N53</t>
+  </si>
+  <si>
+    <t>N54</t>
+  </si>
+  <si>
+    <t>N55</t>
+  </si>
+  <si>
+    <t>N56</t>
+  </si>
+  <si>
+    <t>N57</t>
+  </si>
+  <si>
+    <t>N58</t>
+  </si>
+  <si>
+    <t>N59</t>
+  </si>
+  <si>
+    <t>N60</t>
   </si>
 </sst>
 </file>
@@ -482,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -645,6 +735,156 @@
         <v>31</v>
       </c>
     </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
